--- a/Other/Sounds.xlsx
+++ b/Other/Sounds.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/623821e34d642ca0/Desktop/ASVGC-25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/623821e34d642ca0/Desktop/ASVGC-25/Other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{8189D8F4-1E64-4DF1-B2A6-68F1B77D596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0875F7D-48A9-4C0A-A146-AD34622D5D66}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{8189D8F4-1E64-4DF1-B2A6-68F1B77D596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8013C73C-A333-403F-8172-AAA97A9F18EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{53BCC81A-2A92-4691-9841-E4BA723E9FDD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>URL</t>
   </si>
@@ -53,46 +53,43 @@
     <t>Description / Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">https://freesound.org/people/AugustSandberg/sounds/264864/ </t>
-  </si>
-  <si>
-    <t>https://freesound.org/people/F.M.Audio/sounds/620830/</t>
-  </si>
-  <si>
     <t>CC-BY</t>
   </si>
   <si>
-    <t xml:space="preserve"> https://freesound.org/s/264864/ </t>
-  </si>
-  <si>
     <t>Low Metal Thud 2.wav by F.M.Audio -- License: Attribution 4.0</t>
   </si>
   <si>
     <t>Marine diesel engine by AugustSandberg -- License: Creative Commons 0</t>
   </si>
   <si>
-    <t>https://freesound.org/s/620830/</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
     <t>Low Metal Thud (in the dmg sound)</t>
   </si>
   <si>
     <t>Marine Disel Engine (in the player bote)</t>
   </si>
   <si>
-    <t>https://freesound.org/people/Benboncan/sounds/84111/</t>
-  </si>
-  <si>
     <t>Wind</t>
   </si>
   <si>
     <t>Wind On Door Short.wav by Benboncan  -- License: Attribution 4.0</t>
   </si>
   <si>
-    <t>https://freesound.org/s/84111/</t>
+    <t>Thunder</t>
+  </si>
+  <si>
+    <t>Thunderstorm_Lightning_RX_No_Birds by johnnydekk  -- License: Creative Commons 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://freesound.org/s/686207/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://freesound.org/s/620830/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://freesound.org/s/84111/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://freesound.org/s/264864/ </t>
   </si>
 </sst>
 </file>
@@ -187,6 +184,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,17 +507,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFFBA9D-9989-4AF2-B6F6-460B4EA90217}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="2" max="2" width="35.6640625" customWidth="1"/>
     <col min="3" max="3" width="65.5546875" customWidth="1"/>
     <col min="4" max="4" width="88.44140625" customWidth="1"/>
-    <col min="5" max="5" width="52.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -529,59 +529,61 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D5" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -597,9 +599,10 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{435F98E6-A5DA-4910-A772-3DC6D6D53A7E}"/>
-    <hyperlink ref="C3" r:id="rId2" tooltip="https://freesound.org/people/F.M.Audio/sounds/620830/" xr:uid="{C5B6E2F8-A0DC-484D-880D-75131719CAB8}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{69FF51DC-8DAC-49A3-B169-588A7D4BF72A}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{0158E3DF-0600-452D-B945-796FD3018698}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{51859B73-9F63-4615-85D1-44D1B18D7570}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{F5E223EA-D5CB-4DAB-9AE2-82EDA7F4EFBE}"/>
+    <hyperlink ref="C2" r:id="rId4" xr:uid="{E172B9F3-9AE8-4644-A6A2-4FE4D2378779}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Other/Sounds.xlsx
+++ b/Other/Sounds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/623821e34d642ca0/Desktop/ASVGC-25/Other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{8189D8F4-1E64-4DF1-B2A6-68F1B77D596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8013C73C-A333-403F-8172-AAA97A9F18EF}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{8189D8F4-1E64-4DF1-B2A6-68F1B77D596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F11BE50-D9C3-4ACE-9637-F5DE17D898A9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{53BCC81A-2A92-4691-9841-E4BA723E9FDD}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{53BCC81A-2A92-4691-9841-E4BA723E9FDD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
